--- a/forms/trg/Formulir_TRG_coastal-sr.xlsx
+++ b/forms/trg/Formulir_TRG_coastal-sr.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B19)</f>
+        <f>COUNTA(Anggota!B5:B20)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F19)</f>
+        <f>COUNTA(Anggota!F5:F20)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,12 +925,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Andi Luthfia Amalya</t>
+          <t>Prof. Dr. Ir. Idawarni Asmal, MT (NIP. 196507011994032001)</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Ismah Qosimah</t>
+          <t>Andi Luthfia Amalya</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Andi Muhammad Ikhsan</t>
+          <t>Ismah Qosimah</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1010,8 +1010,16 @@
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Andi Muhammad Ikhsan</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
@@ -1021,7 +1029,11 @@
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
+      <c r="M8" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1210,15 +1222,32 @@
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="12" t="n"/>
     </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
